--- a/automation/reports/appium/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/appium/Excel/Automation_Test_Report.xlsx
@@ -1881,7 +1881,7 @@
     <t>Run Stamp</t>
   </si>
   <si>
-    <t>2026-07-26T15-23-20-316Z</t>
+    <t>2026-07-26T17-40-12-404Z</t>
   </si>
   <si>
     <t>Total Cases</t>

--- a/automation/reports/appium/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/appium/Excel/Automation_Test_Report.xlsx
@@ -2069,7 +2069,7 @@
     <t>Run Stamp</t>
   </si>
   <si>
-    <t>2026-07-27T06-47-17-989Z</t>
+    <t>2026-07-27T06-53-32-278Z</t>
   </si>
   <si>
     <t>Total Cases</t>

--- a/automation/reports/appium/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/appium/Excel/Automation_Test_Report.xlsx
@@ -2069,7 +2069,7 @@
     <t>Run Stamp</t>
   </si>
   <si>
-    <t>2026-07-27T06-53-32-278Z</t>
+    <t>2026-07-27T07-08-36-051Z</t>
   </si>
   <si>
     <t>Total Cases</t>
